--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484827_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484827_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1029</v>
+        <v>-0.3911</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2683</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1653</v>
+        <v>0.3241</v>
       </c>
       <c r="G2" t="n">
         <v>-0.285</v>
@@ -610,13 +610,13 @@
         <v>0.5661</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2386</v>
+        <v>-0.0495</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6525</v>
+        <v>0.2056</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4138</v>
+        <v>-0.2551</v>
       </c>
       <c r="V2" t="n">
         <v>0.3208</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>P. OSAWARU CUENCA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.4463</v>
+        <v>-1.0663</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.102</v>
+        <v>-1.7408</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3444</v>
+        <v>0.6746</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6127</v>
+        <v>-0.2783</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.494</v>
+        <v>0.133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8813</v>
+        <v>-0.4113</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8895</v>
+        <v>-0.5807</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7662</v>
+        <v>0.0689</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1234</v>
+        <v>-0.6496</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5022</v>
+        <v>0.3024</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2601</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7579</v>
+        <v>0.2383</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1663</v>
+        <v>-0.788</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5937</v>
+        <v>-0.2166</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4273</v>
+        <v>-0.5714</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. OSAWARU CUENCA</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.6285</v>
+        <v>-1.8663</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.1709</v>
+        <v>-0.6278</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5423</v>
+        <v>-1.2385</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2783</v>
+        <v>-0.6127</v>
       </c>
       <c r="H4" t="n">
-        <v>0.133</v>
+        <v>-1.494</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4113</v>
+        <v>0.8813</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5807</v>
+        <v>0.8895</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0689</v>
+        <v>0.7662</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6496</v>
+        <v>0.1234</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3024</v>
+        <v>-1.5022</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06419999999999999</v>
+        <v>-2.2601</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2383</v>
+        <v>0.7579</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3503</v>
+        <v>-0.2537</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.0679</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7036</v>
+        <v>-0.3215</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6574</v>
+        <v>-1.987</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9024</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5984</v>
+        <v>-2.8894</v>
       </c>
       <c r="G5" t="n">
         <v>-1.206</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5485</v>
+        <v>0.2188</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0646</v>
+        <v>0.0259</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4839</v>
+        <v>0.1929</v>
       </c>
       <c r="V5" t="n">
         <v>-1.566</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3832</v>
+        <v>-1.9893</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0411</v>
+        <v>-0.806</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3421</v>
+        <v>-1.1833</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8736</v>
@@ -922,13 +922,13 @@
         <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.3233</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.585</v>
+        <v>-0.3498</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1322</v>
+        <v>0.0265</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6036</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. TORMO HERRERO</t>
+          <t>F. LOPEZ ZOROA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4945</v>
+        <v>-2.3265</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.627</v>
+        <v>-2.3919</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8676</v>
+        <v>0.0655</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0867</v>
+        <v>-2.7039</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.8199</v>
+        <v>-1.5738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2669</v>
+        <v>-1.1301</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1506</v>
+        <v>-1.7655</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1949</v>
+        <v>0.1009</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9557</v>
+        <v>-1.8664</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9361</v>
+        <v>-0.9384</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.625</v>
+        <v>-1.6747</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6889</v>
+        <v>0.7363</v>
       </c>
       <c r="P7" t="n">
         <v>0.1887</v>
@@ -1000,19 +1000,19 @@
         <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4791</v>
+        <v>0.1887</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2409</v>
+        <v>0.0152</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2381</v>
+        <v>0.1735</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2262</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
         <v>-0.3018</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. NAVARRO MORALES</t>
+          <t>P. TORMO HERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2573</v>
+        <v>-2.71</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7186</v>
+        <v>-1.763</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5387</v>
+        <v>-0.947</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9185</v>
+        <v>-4.0867</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4793</v>
+        <v>-3.8199</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5608</v>
+        <v>-0.2669</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8933</v>
+        <v>-2.1506</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9344</v>
+        <v>-0.1949</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0411</v>
+        <v>-1.9557</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0252</v>
+        <v>-1.9361</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5448</v>
+        <v>-3.625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5196</v>
+        <v>1.6889</v>
       </c>
       <c r="P8" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9435</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.887</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0935</v>
+        <v>0.2636</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0617</v>
+        <v>0.1049</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1552</v>
+        <v>0.1588</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3018</v>
+        <v>0.9244</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X8" t="n">
         <v>-0.3018</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. LOPEZ ZOROA</t>
+          <t>J. NAVARRO MORALES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3529</v>
+        <v>-2.8777</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5241</v>
+        <v>-2.4448</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1713</v>
+        <v>-0.4328</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7039</v>
+        <v>-1.9185</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5738</v>
+        <v>-2.4793</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1301</v>
+        <v>0.5608</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7655</v>
+        <v>-0.8933</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1009</v>
+        <v>-0.9344</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8664</v>
+        <v>0.0411</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9384</v>
+        <v>-1.0252</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6747</v>
+        <v>-1.5448</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7363</v>
+        <v>0.5196</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8377</v>
+        <v>0.2861</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.117</v>
+        <v>0.3355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2793</v>
+        <v>-0.0493</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.3018</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3432</v>
+        <v>-3.9451</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6068</v>
+        <v>-2.3145</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7364</v>
+        <v>-1.6306</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3379</v>
@@ -1234,13 +1234,13 @@
         <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2504</v>
+        <v>-0.8522</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7642</v>
+        <v>-0.4719</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4861</v>
+        <v>-0.3803</v>
       </c>
       <c r="V10" t="n">
         <v>2.1886</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.8401</v>
+        <v>-7.5835</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1673</v>
+        <v>-3.6197</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.6728</v>
+        <v>-3.9638</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9276</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4785</v>
+        <v>-0.2219</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7613</v>
+        <v>-0.2137</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2828</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.547</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-28.5063</v>
+        <v>-26.7428</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.2851</v>
+        <v>-15.5213</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.2215</v>
+        <v>-11.2212</v>
       </c>
       <c r="G12" t="n">
         <v>-20.2302</v>
@@ -1378,7 +1378,7 @@
         <v>-19.6742</v>
       </c>
       <c r="O12" t="n">
-        <v>5.522600000000001</v>
+        <v>5.5226</v>
       </c>
       <c r="P12" t="n">
         <v>-3.774</v>
@@ -1390,10 +1390,10 @@
         <v>10.3785</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2951</v>
+        <v>-1.5314</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2608</v>
+        <v>-0.497</v>
       </c>
       <c r="U12" t="n">
         <v>-1.0341</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.8629</v>
+        <v>8.6248</v>
       </c>
       <c r="E13" t="n">
         <v>6.0462</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8167</v>
+        <v>2.5786</v>
       </c>
       <c r="G13" t="n">
         <v>5.029</v>
@@ -1468,13 +1468,13 @@
         <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6643</v>
+        <v>0.4262</v>
       </c>
       <c r="T13" t="n">
         <v>0.1205</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5438</v>
+        <v>0.3057</v>
       </c>
       <c r="V13" t="n">
         <v>2.7922</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6711</v>
+        <v>7.8659</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6203</v>
+        <v>5.8152</v>
       </c>
       <c r="F14" t="n">
         <v>2.0508</v>
@@ -1546,10 +1546,10 @@
         <v>2.4531</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.037</v>
+        <v>0.1579</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09</v>
+        <v>0.1049</v>
       </c>
       <c r="U14" t="n">
         <v>0.053</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8924</v>
+        <v>5.2724</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2971</v>
+        <v>1.492</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5953</v>
+        <v>3.7804</v>
       </c>
       <c r="G15" t="n">
         <v>3.6255</v>
@@ -1624,13 +1624,13 @@
         <v>2.8305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3374</v>
+        <v>0.0426</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3963</v>
+        <v>-0.2014</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0589</v>
+        <v>0.2441</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2262</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5254</v>
+        <v>3.3575</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4109</v>
+        <v>0.534</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1145</v>
+        <v>2.8235</v>
       </c>
       <c r="G16" t="n">
         <v>3.5385</v>
@@ -1702,13 +1702,13 @@
         <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9869</v>
+        <v>0.819</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1968</v>
+        <v>0.3199</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7902</v>
+        <v>0.4992</v>
       </c>
       <c r="V16" t="n">
         <v>0.3208</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0387</v>
+        <v>2.4012</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3136</v>
+        <v>-0.8982</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3523</v>
+        <v>3.2994</v>
       </c>
       <c r="G17" t="n">
         <v>1.962</v>
@@ -1780,13 +1780,13 @@
         <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8124</v>
+        <v>0.1749</v>
       </c>
       <c r="T17" t="n">
-        <v>0.606</v>
+        <v>0.0214</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2064</v>
+        <v>0.1535</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3018</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8546</v>
+        <v>1.1107</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.373</v>
+        <v>-0.2755</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2276</v>
+        <v>1.3863</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3891</v>
@@ -1858,13 +1858,13 @@
         <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6966</v>
+        <v>0.9528</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3803</v>
+        <v>0.4777</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3163</v>
+        <v>0.475</v>
       </c>
       <c r="V18" t="n">
         <v>0.6036</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ó. GONZÁLEZ JURADO</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.317</v>
+        <v>0.3537</v>
       </c>
       <c r="E19" t="n">
-        <v>0.317</v>
+        <v>0.1605</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.1932</v>
       </c>
       <c r="G19" t="n">
-        <v>0.317</v>
+        <v>2.5328</v>
       </c>
       <c r="H19" t="n">
-        <v>0.317</v>
+        <v>3.0263</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.4936</v>
       </c>
       <c r="J19" t="n">
-        <v>0.317</v>
+        <v>2.6475</v>
       </c>
       <c r="K19" t="n">
-        <v>0.317</v>
+        <v>2.5567</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.1148</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.4696</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.5843</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.2738</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2323</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8868</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>Ó. GONZÁLEZ JURADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3093</v>
+        <v>0.317</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0166</v>
+        <v>0.317</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2928</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2923</v>
+        <v>0.317</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2232</v>
+        <v>0.317</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4281</v>
+        <v>0.317</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0776</v>
+        <v>0.317</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1358</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1456</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2814</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7719</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2399</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2393</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3267</v>
+        <v>-0.045</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.0521</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5328</v>
+        <v>-0.2363</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0263</v>
+        <v>0.0039</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4936</v>
+        <v>-0.2403</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6475</v>
+        <v>-0.376</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5567</v>
+        <v>0.2324</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1148</v>
+        <v>0.1397</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4696</v>
+        <v>-0.2285</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5843</v>
+        <v>0.3682</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3192</v>
+        <v>0.3279</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4456</v>
+        <v>0.0292</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1264</v>
+        <v>0.2987</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8868</v>
+        <v>-0.9434</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="X21" t="n">
         <v>-1.2452</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8488</v>
+        <v>-0.1153</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5322</v>
+        <v>-0.2757</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3166</v>
+        <v>0.1605</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2363</v>
+        <v>0.2923</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0039</v>
+        <v>1.2232</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2403</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.376</v>
+        <v>0.4281</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2324</v>
+        <v>1.0776</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6496</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1397</v>
+        <v>-0.1358</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2285</v>
+        <v>0.1456</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3682</v>
+        <v>-0.2814</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7548</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4238</v>
+        <v>0.3473</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.458</v>
+        <v>0.2397</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0341</v>
+        <v>0.1076</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9434</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8768</v>
+        <v>-0.5845</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9412</v>
+        <v>-1.6489</v>
       </c>
       <c r="F23" t="n">
         <v>1.0644</v>
@@ -2248,10 +2248,10 @@
         <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5196</v>
+        <v>-0.2273</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4115</v>
+        <v>-0.1192</v>
       </c>
       <c r="U23" t="n">
         <v>-0.1081</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>28.5065</v>
+        <v>28.5063</v>
       </c>
       <c r="E24" t="n">
-        <v>11.2214</v>
+        <v>11.2216</v>
       </c>
       <c r="F24" t="n">
-        <v>17.2852</v>
+        <v>17.285</v>
       </c>
       <c r="G24" t="n">
         <v>20.2304</v>
@@ -2305,7 +2305,7 @@
         <v>19.6742</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.522600000000001</v>
+        <v>-5.522599999999999</v>
       </c>
       <c r="M24" t="n">
         <v>6.0784</v>
@@ -2332,13 +2332,13 @@
         <v>1.0342</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2609</v>
+        <v>2.261</v>
       </c>
       <c r="V24" t="n">
         <v>1.2072</v>
       </c>
       <c r="W24" t="n">
-        <v>6.4138</v>
+        <v>6.413799999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-5.2066</v>
